--- a/Packages/cn.etetet.equipment/Luban/Config/Datas/Equipment.xlsx
+++ b/Packages/cn.etetet.equipment/Luban/Config/Datas/Equipment.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.equipment/Luban/Config/Datas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9938625-CFAD-EE4F-8986-8839DB5A235B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17820" yWindow="8100" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentConfig" sheetId="1" r:id="rId1"/>
@@ -33,14 +27,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>EquipSlot</t>
+  </si>
+  <si>
+    <t>KV</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -50,12 +56,21 @@
     <t>string</t>
   </si>
   <si>
+    <t>map,int,long</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
-    <t>Desc</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -65,102 +80,56 @@
     <t>描述</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>EquipSlot</t>
-  </si>
-  <si>
     <t>装备部位</t>
   </si>
   <si>
-    <t>新手之剑</t>
-  </si>
-  <si>
-    <t>适合初学者使用的铁剑</t>
-  </si>
-  <si>
-    <t>皮革头盔</t>
-  </si>
-  <si>
-    <t>简单的皮革头盔</t>
-  </si>
-  <si>
-    <t>铁制胸甲</t>
-  </si>
-  <si>
-    <t>坚固的铁制护甲</t>
-  </si>
-  <si>
-    <t>布袍</t>
-  </si>
-  <si>
-    <t>法师的入门长袍</t>
-  </si>
-  <si>
-    <t>皮革护腿</t>
-  </si>
-  <si>
-    <t>适合游侠的护腿</t>
-  </si>
-  <si>
-    <t>铁靴</t>
-  </si>
-  <si>
-    <t>厚重的战士之靴</t>
-  </si>
-  <si>
-    <t>精灵之弓</t>
-  </si>
-  <si>
-    <t>轻盈的远程武器</t>
-  </si>
-  <si>
-    <t>魔法项链</t>
-  </si>
-  <si>
-    <t>增强魔法的项链</t>
-  </si>
-  <si>
-    <t>力量戒指</t>
-  </si>
-  <si>
-    <t>增加力量的戒指</t>
-  </si>
-  <si>
-    <t>KV</t>
-  </si>
-  <si>
-    <t>map,int,long</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>速度Base</t>
   </si>
   <si>
+    <t>MaxHPBase</t>
+  </si>
+  <si>
     <t>MaxMPPct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHPBase</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>##group</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>霰弹枪1号</t>
+  </si>
+  <si>
+    <t>射程近，散射4发</t>
+  </si>
+  <si>
+    <t>步枪1号</t>
+  </si>
+  <si>
+    <t>强制追踪，伤害高</t>
+  </si>
+  <si>
+    <t>步枪2号</t>
+  </si>
+  <si>
+    <t>方向锁定，射程远</t>
+  </si>
+  <si>
+    <t>火箭炮1号</t>
+  </si>
+  <si>
+    <t>位置锁定，爆炸伤害</t>
+  </si>
+  <si>
+    <t>冲锋枪</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,25 +142,160 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,8 +314,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -219,38 +509,324 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -508,22 +1084,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="7.83333333333333" customWidth="1"/>
+    <col min="3" max="3" width="9.33333333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="10.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="8.66666666666667" customWidth="1"/>
+    <col min="7" max="7" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -531,400 +1107,257 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1"/>
-      <c r="F3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="B5" s="2">
-        <v>10004</v>
+      <c r="B5">
+        <v>50009</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I5" s="6">
-        <v>100</v>
-      </c>
-      <c r="J5" s="6">
+        <v>6</v>
+      </c>
+      <c r="F5">
         <v>10041</v>
       </c>
-      <c r="K5" s="6">
+      <c r="G5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="2">
-        <v>10005</v>
+      <c r="B6">
+        <v>50010</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G6" s="6">
-        <v>6000</v>
-      </c>
-      <c r="H6" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10041</v>
       </c>
-      <c r="K6" s="6">
-        <v>1000</v>
+      <c r="G6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="2">
-        <v>10006</v>
+      <c r="B7">
+        <v>50011</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G7" s="6">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>10041</v>
+      </c>
+      <c r="G7">
         <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I7" s="6">
-        <v>100</v>
-      </c>
-      <c r="J7" s="6">
-        <v>10041</v>
-      </c>
-      <c r="K7" s="6">
-        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="2">
-        <v>10007</v>
+      <c r="B8">
+        <v>50012</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G8" s="6">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>10041</v>
+      </c>
+      <c r="G8">
         <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I8" s="6">
-        <v>100</v>
-      </c>
-      <c r="J8" s="6">
-        <v>10041</v>
-      </c>
-      <c r="K8" s="6">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="2">
-        <v>10008</v>
+      <c r="B9">
+        <v>50013</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H9" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I9" s="6">
-        <v>100</v>
-      </c>
-      <c r="J9" s="6">
+        <v>6</v>
+      </c>
+      <c r="F9">
         <v>10041</v>
       </c>
-      <c r="K9" s="6">
-        <v>100</v>
+      <c r="G9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="2">
-        <v>10009</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G10" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H10" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I10" s="6">
-        <v>100</v>
-      </c>
-      <c r="J10" s="6">
-        <v>10041</v>
-      </c>
-      <c r="K10" s="6">
-        <v>100</v>
-      </c>
+      <c r="B10" s="5"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="2">
-        <v>10010</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G11" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H11" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I11" s="6">
-        <v>100</v>
-      </c>
-      <c r="J11" s="6">
-        <v>10041</v>
-      </c>
-      <c r="K11" s="6">
-        <v>100</v>
-      </c>
+      <c r="B11" s="5"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="B12" s="2">
-        <v>10011</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12">
-        <v>7</v>
-      </c>
-      <c r="F12" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G12" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H12" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I12" s="6">
-        <v>100</v>
-      </c>
-      <c r="J12" s="6">
-        <v>10041</v>
-      </c>
-      <c r="K12" s="6">
-        <v>100</v>
-      </c>
+      <c r="B12" s="5"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="2">
-        <v>10012</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13" s="6">
-        <v>10001</v>
-      </c>
-      <c r="G13" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H13" s="6">
-        <v>10021</v>
-      </c>
-      <c r="I13" s="6">
-        <v>100</v>
-      </c>
-      <c r="J13" s="6">
-        <v>10041</v>
-      </c>
-      <c r="K13" s="6">
-        <v>100</v>
-      </c>
+      <c r="B13" s="5"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="J4:K4"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="F2:K2"/>
+    <mergeCell ref="F3:K3"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="F3:K3"/>
+    <mergeCell ref="J4:K4"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Packages/cn.etetet.equipment/Luban/Config/Datas/Equipment.xlsx
+++ b/Packages/cn.etetet.equipment/Luban/Config/Datas/Equipment.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="EquipmentConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -117,6 +117,30 @@
   </si>
   <si>
     <t>冲锋枪</t>
+  </si>
+  <si>
+    <t>轻型防弹衣 I</t>
+  </si>
+  <si>
+    <t>基础护甲，提供少量生命加成，适合新手起装</t>
+  </si>
+  <si>
+    <t>侦察护甲 II</t>
+  </si>
+  <si>
+    <t>兼顾生存与机动的中级护甲，适合常规跑局</t>
+  </si>
+  <si>
+    <t>突击护甲 III</t>
+  </si>
+  <si>
+    <t>更厚重的突击护甲，适合正面作战</t>
+  </si>
+  <si>
+    <t>重型护甲 IV</t>
+  </si>
+  <si>
+    <t>高等级重型护甲，大幅提升生存能力</t>
   </si>
 </sst>
 </file>
@@ -610,165 +634,165 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="6" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="7" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="34" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,7 +1112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -1102,7 +1126,7 @@
     <col min="7" max="7" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1151,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,7 +1176,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1173,7 +1197,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1202,153 +1226,201 @@
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5">
+    <row r="5">
+      <c r="B5" s="0">
         <v>50009</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>10041</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6">
+    <row r="6">
+      <c r="B6" s="0">
         <v>50010</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>10041</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7">
+    <row r="7">
+      <c r="B7" s="0">
         <v>50011</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <v>6</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>10041</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="B8">
+    <row r="8">
+      <c r="B8" s="0">
         <v>50012</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="0">
         <v>6</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>10041</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="B9">
+    <row r="9">
+      <c r="B9" s="0">
         <v>50013</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <v>6</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <v>10041</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="5"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+    <row r="10">
+      <c r="B10" s="5">
+        <v>20001</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="0">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>10021</v>
+      </c>
+      <c r="G10" s="6">
+        <v>40</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="5"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+    <row r="11">
+      <c r="B11" s="5">
+        <v>20002</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="0">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6">
+        <v>10021</v>
+      </c>
+      <c r="G11" s="6">
+        <v>75</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="5"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+    <row r="12">
+      <c r="B12" s="5">
+        <v>20003</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="0">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>10021</v>
+      </c>
+      <c r="G12" s="6">
+        <v>125</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="5"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+    <row r="13">
+      <c r="B13" s="5">
+        <v>20004</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="0">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6">
+        <v>10021</v>
+      </c>
+      <c r="G13" s="6">
+        <v>180</v>
+      </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="F3:K3"/>
@@ -1360,4 +1432,9 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>